--- a/receipt_1.xlsx
+++ b/receipt_1.xlsx
@@ -436,14 +436,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Funko Pop Spider-Man</t>
+          <t>Funko Pop Iron Man</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>39.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.99</v>
+        <v>224.95</v>
       </c>
     </row>
   </sheetData>
